--- a/data/trans_camb/P44-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P44-Edad-trans_camb.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -593,32 +593,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56,16</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,68</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42,2</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,49; 6,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,17; 83,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,34; 0,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,97; 22,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,64; 1,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,48; 69,73</t>
         </is>
       </c>
     </row>
@@ -669,32 +669,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>929,61%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-51,71%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>243,93%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-12,5%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>635,88%</t>
         </is>
       </c>
     </row>
@@ -707,39 +707,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-32,77; 180,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>324,36; 3676,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,23; 14,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>110,94; 482,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-45,64; 39,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>269,69; 1612,21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24,39</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23,46</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,67; 6,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,44; 29,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,82; 3,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,05; 26,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,26; 3,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,15; 26,5</t>
         </is>
       </c>
     </row>
@@ -825,32 +825,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>256,74%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-3,58%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>283,57%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>270,52%</t>
         </is>
       </c>
     </row>
@@ -863,39 +863,39 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-23,13; 90,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>158,23; 416,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-39,62; 57,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>168,57; 478,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,94; 49,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>195,9; 390,22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -905,32 +905,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35,01</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14,46</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22,06</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,65; 7,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,74; 40,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,2; 3,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,84; 28,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,78; 3,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,97; 32,54</t>
         </is>
       </c>
     </row>
@@ -981,32 +981,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>321,5%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-7,73%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>151,59%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>217,07%</t>
         </is>
       </c>
     </row>
@@ -1019,39 +1019,39 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-26,57; 98,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>192,12; 529,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-43,22; 44,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-19,54; 321,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,6; 46,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,26; 357,27</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1061,32 +1061,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>4,62</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>56,16</t>
+          <t>24,93</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,68</t>
+          <t>3,8</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,37</t>
+          <t>21,42</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,2</t>
+          <t>22,95</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,65</t>
+          <t>-2,08; 9,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,81; 82,0</t>
+          <t>18,06; 30,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -0,25</t>
+          <t>0,05; 8,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,51; 22,31</t>
+          <t>17,55; 25,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,07</t>
+          <t>0,69; 7,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,65; 72,71</t>
+          <t>19,42; 26,33</t>
         </is>
       </c>
     </row>
@@ -1137,32 +1137,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>929,61%</t>
+          <t>221,76%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-51,71%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>243,93%</t>
+          <t>390,08%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-12,5%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>635,88%</t>
+          <t>297,48%</t>
         </is>
       </c>
     </row>
@@ -1175,39 +1175,39 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 201,58</t>
+          <t>-14,98; 119,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>353,15; 4132,33</t>
+          <t>115,52; 385,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,56; 0,5</t>
+          <t>-1,94; 209,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119,93; 458,66</t>
+          <t>220,55; 722,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,51; 45,35</t>
+          <t>5,97; 121,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>275,62; 1660,8</t>
+          <t>192,95; 435,35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1217,32 +1217,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24,39</t>
+          <t>36,12</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>19,02</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,46</t>
+          <t>27,4</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 5,87</t>
+          <t>-0,21; 4,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19,26; 28,94</t>
+          <t>25,9; 55,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,57</t>
+          <t>-1,97; 1,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18,16; 26,13</t>
+          <t>9,33; 22,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,58</t>
+          <t>-0,6; 2,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,17; 26,72</t>
+          <t>20,61; 40,95</t>
         </is>
       </c>
     </row>
@@ -1293,32 +1293,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>256,74%</t>
+          <t>379,09%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-3,58%</t>
+          <t>-0,32%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>283,57%</t>
+          <t>253,56%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>270,52%</t>
+          <t>325,88%</t>
         </is>
       </c>
     </row>
@@ -1331,523 +1331,52 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 85,87</t>
+          <t>-2,49; 56,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>154,57; 422,28</t>
+          <t>252,2; 661,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,91; 61,89</t>
+          <t>-23,62; 29,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>168,25; 450,62</t>
+          <t>140,99; 342,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 52,16</t>
+          <t>-5,74; 36,06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>186,16; 380,82</t>
+          <t>233,98; 505,67</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>35,01</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-0,74</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>14,46</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>22,06</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n"/>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>-3,43; 7,51</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>28,85; 40,49</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>-4,9; 3,68</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>-0,42; 28,63</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>-2,47; 4,09</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,46; 31,96</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>23,43%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>321,5%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-7,73%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>151,59%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>217,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>-25,8; 97,03</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>180,47; 534,5</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-41,82; 50,02</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>-3,76; 325,38</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-21,23; 49,45</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>66,43; 338,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>4,62</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>24,93</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3,8</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>21,42</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>4,15</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>22,95</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>-1,33; 10,7</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>17,81; 31,05</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>-0,1; 7,9</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>17,21; 24,79</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>0,71; 7,73</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>19,18; 26,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>41,08%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>221,76%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>69,24%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>390,08%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>53,73%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>297,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>-9,93; 133,5</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>110,78; 392,42</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>-8,96; 189,22</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>216,78; 683,35</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>6,77; 125,74</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>202,26; 446,04</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>2,25</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>36,12</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>19,02</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>1,08</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>27,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n"/>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>-0,22; 4,69</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>26,39; 56,99</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>-1,92; 1,8</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>10,15; 23,23</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>-0,68; 2,54</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>21,08; 40,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n"/>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>23,65%</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>379,09%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-0,32%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>253,56%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>12,81%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>325,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>-2,36; 57,89</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>260,36; 647,21</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>-22,95; 27,72</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>137,19; 336,2</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>-7,29; 34,17</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>234,27; 487,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A32:A35"/>
+  <mergeCells count="9">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A24:A27"/>
     <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_camb/P44-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P44-Edad-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>56,16</t>
+          <t>24,61</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,37</t>
+          <t>17,62</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,2</t>
+          <t>21,05</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 6,4</t>
+          <t>-2,64; 6,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,17; 83,19</t>
+          <t>17,73; 30,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 0,21</t>
+          <t>-7,75; -0,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,97; 22,36</t>
+          <t>12,62; 22,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,89</t>
+          <t>-3,78; 2,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,48; 69,73</t>
+          <t>16,73; 24,81</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>929,61%</t>
+          <t>407,4%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>243,93%</t>
+          <t>247,43%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>635,88%</t>
+          <t>317,18%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 180,46</t>
+          <t>-33,49; 175,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>324,36; 3676,77</t>
+          <t>176,11; 876,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-78,23; 14,23</t>
+          <t>-78,82; 3,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110,94; 482,61</t>
+          <t>121,53; 452,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,64; 39,86</t>
+          <t>-46,25; 40,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>269,69; 1612,21</t>
+          <t>194,66; 518,45</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24,39</t>
+          <t>23,53</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>22,56</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,46</t>
+          <t>23,09</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 6,22</t>
+          <t>-3,25; 5,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,44; 29,09</t>
+          <t>18,38; 27,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 3,41</t>
+          <t>-4,15; 3,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,05; 26,38</t>
+          <t>18,61; 26,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,48</t>
+          <t>-2,09; 3,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,15; 26,5</t>
+          <t>19,65; 26,31</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>256,74%</t>
+          <t>247,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>283,57%</t>
+          <t>285,64%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>270,52%</t>
+          <t>266,15%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 90,52</t>
+          <t>-27,64; 77,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>158,23; 416,92</t>
+          <t>148,07; 381,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,62; 57,38</t>
+          <t>-43,4; 55,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>168,57; 478,31</t>
+          <t>175,96; 466,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 49,35</t>
+          <t>-20,31; 48,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>195,9; 390,22</t>
+          <t>180,28; 379,45</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35,01</t>
+          <t>34,16</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,46</t>
+          <t>27,56</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,06</t>
+          <t>30,77</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 7,81</t>
+          <t>-3,49; 7,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,74; 40,44</t>
+          <t>27,79; 39,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 3,3</t>
+          <t>-5,23; 3,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 28,11</t>
+          <t>22,98; 31,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 3,99</t>
+          <t>-2,76; 4,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 32,54</t>
+          <t>26,97; 34,66</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>321,5%</t>
+          <t>313,73%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151,59%</t>
+          <t>289,02%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>217,07%</t>
+          <t>302,86%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,57; 98,38</t>
+          <t>-25,72; 98,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>192,12; 529,81</t>
+          <t>175,63; 507,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 44,97</t>
+          <t>-44,57; 45,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 321,77</t>
+          <t>180,75; 463,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 46,33</t>
+          <t>-22,88; 49,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63,26; 357,27</t>
+          <t>214,71; 430,63</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24,93</t>
+          <t>24,68</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,42</t>
+          <t>21,82</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,95</t>
+          <t>23,1</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 9,76</t>
+          <t>-1,6; 10,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,06; 30,92</t>
+          <t>18,01; 30,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 8,28</t>
+          <t>-0,2; 7,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,55; 25,31</t>
+          <t>17,95; 25,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,54</t>
+          <t>0,85; 7,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,42; 26,33</t>
+          <t>19,3; 26,32</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>221,76%</t>
+          <t>219,53%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>390,08%</t>
+          <t>397,5%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>297,48%</t>
+          <t>299,47%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 119,53</t>
+          <t>-13,05; 125,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>115,52; 385,09</t>
+          <t>115,33; 382,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 209,18</t>
+          <t>-4,87; 206,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>220,55; 722,12</t>
+          <t>230,27; 751,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,97; 121,25</t>
+          <t>6,34; 115,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>192,95; 435,35</t>
+          <t>195,52; 439,16</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>36,12</t>
+          <t>26,58</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19,02</t>
+          <t>22,76</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>24,63</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 4,71</t>
+          <t>-0,38; 4,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25,9; 55,91</t>
+          <t>23,7; 29,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,96</t>
+          <t>-2,1; 1,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,33; 22,98</t>
+          <t>20,62; 25,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,69</t>
+          <t>-0,63; 2,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,61; 40,95</t>
+          <t>22,86; 26,44</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>379,09%</t>
+          <t>278,95%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>253,56%</t>
+          <t>303,47%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>325,88%</t>
+          <t>292,94%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 56,63</t>
+          <t>-4,16; 58,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>252,2; 661,52</t>
+          <t>207,12; 366,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 29,74</t>
+          <t>-25,54; 29,36</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>140,99; 342,01</t>
+          <t>231,93; 400,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 36,06</t>
+          <t>-6,98; 34,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>233,98; 505,67</t>
+          <t>239,76; 354,41</t>
         </is>
       </c>
     </row>
